--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444666370446814</v>
       </c>
       <c r="C2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>27735541</v>
+        <v>4305976</v>
       </c>
       <c r="L2" t="n">
-        <v>16014390</v>
+        <v>2166166</v>
       </c>
       <c r="M2" t="n">
-        <v>4029791</v>
+        <v>477754</v>
       </c>
       <c r="N2" t="n">
-        <v>228317</v>
+        <v>17556</v>
       </c>
       <c r="O2" t="n">
-        <v>2369440</v>
+        <v>275088</v>
       </c>
       <c r="P2" t="n">
-        <v>948358</v>
+        <v>112996</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999894499778748</v>
+        <v>0.999994158744812</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9016380906105042</v>
+        <v>0.8185819387435913</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8082230687141418</v>
+        <v>0.6667713522911072</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7634031772613525</v>
+        <v>0.5768359303474426</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4302056133747101</v>
+        <v>0.1203908771276474</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8068689107894897</v>
+        <v>0.6301321983337402</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8655286431312561</v>
+        <v>0.7535880208015442</v>
       </c>
       <c r="X2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.95653235912323</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911312997341156</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580047488212585</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.66214919090271</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646644592285</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024449655927808</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>27735541</v>
+        <v>4305976</v>
       </c>
       <c r="E3" t="n">
-        <v>2575044</v>
+        <v>720024</v>
       </c>
       <c r="F3" t="n">
-        <v>44435</v>
+        <v>16772</v>
       </c>
       <c r="G3" t="n">
-        <v>5890</v>
+        <v>1819</v>
       </c>
       <c r="H3" t="n">
-        <v>2459</v>
+        <v>949</v>
       </c>
       <c r="I3" t="n">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="J3" t="n">
-        <v>60417319</v>
+        <v>10069583</v>
       </c>
       <c r="K3" t="n">
-        <v>65106711</v>
+        <v>10416109</v>
       </c>
       <c r="L3" t="n">
-        <v>75001315</v>
+        <v>12038217</v>
       </c>
       <c r="M3" t="n">
-        <v>91640613</v>
+        <v>15129631</v>
       </c>
       <c r="N3" t="n">
-        <v>97657517</v>
+        <v>16198227</v>
       </c>
       <c r="O3" t="n">
-        <v>94872007</v>
+        <v>15744537</v>
       </c>
       <c r="P3" t="n">
-        <v>97188635</v>
+        <v>16185612</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9134485721588135</v>
+        <v>0.8534154891967773</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8131296634674072</v>
+        <v>0.6573681235313416</v>
       </c>
       <c r="T3" t="n">
-        <v>0.718776524066925</v>
+        <v>0.5104804039001465</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4258978068828583</v>
+        <v>0.1961476653814316</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7751255035400391</v>
+        <v>0.5393935441970825</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8175323605537415</v>
+        <v>0.5841397643089294</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1194510</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51498</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>40960</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60417720</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66811145</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77057112</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92093936</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>97778931</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95139602</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97256450</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575998783111572</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099897742271423</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574815392494202</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616687178611755</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015793204307556</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319545241795172</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2858609</v>
+        <v>898077</v>
       </c>
       <c r="E4" t="n">
-        <v>16014390</v>
+        <v>2166166</v>
       </c>
       <c r="F4" t="n">
-        <v>731210</v>
+        <v>197573</v>
       </c>
       <c r="G4" t="n">
-        <v>33993</v>
+        <v>13951</v>
       </c>
       <c r="H4" t="n">
-        <v>51808</v>
+        <v>17687</v>
       </c>
       <c r="I4" t="n">
-        <v>4737</v>
+        <v>1755</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
-        <v>3025739</v>
+        <v>954311</v>
       </c>
       <c r="L4" t="n">
-        <v>3799930</v>
+        <v>1082573</v>
       </c>
       <c r="M4" t="n">
-        <v>1248928</v>
+        <v>350478</v>
       </c>
       <c r="N4" t="n">
-        <v>302399</v>
+        <v>128269</v>
       </c>
       <c r="O4" t="n">
-        <v>567146</v>
+        <v>161468</v>
       </c>
       <c r="P4" t="n">
-        <v>147340</v>
+        <v>36948</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999994695186615</v>
+        <v>0.999997079372406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9075049757957458</v>
+        <v>0.8356359004974365</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8106689453125</v>
+        <v>0.6620363593101501</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7404180765151978</v>
+        <v>0.5416334271430969</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4280408620834351</v>
+        <v>0.1492038816213608</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7906787395477295</v>
+        <v>0.5812428593635559</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8408461213111877</v>
+        <v>0.6581319570541382</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1233664</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>498690</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33091</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6876</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1321305</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1744133</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>795605</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>180985</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299551</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570658206939697</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910650908946991</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577430844306946</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619088649749756</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017719030380249</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>108318</v>
+        <v>39046</v>
       </c>
       <c r="E5" t="n">
-        <v>1054399</v>
+        <v>305066</v>
       </c>
       <c r="F5" t="n">
-        <v>4029791</v>
+        <v>477754</v>
       </c>
       <c r="G5" t="n">
-        <v>108977</v>
+        <v>39429</v>
       </c>
       <c r="H5" t="n">
-        <v>281965</v>
+        <v>66927</v>
       </c>
       <c r="I5" t="n">
-        <v>22990</v>
+        <v>7665</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2628009</v>
+        <v>739604</v>
       </c>
       <c r="L5" t="n">
-        <v>3680365</v>
+        <v>1129044</v>
       </c>
       <c r="M5" t="n">
-        <v>1576668</v>
+        <v>458137</v>
       </c>
       <c r="N5" t="n">
-        <v>307767</v>
+        <v>71948</v>
       </c>
       <c r="O5" t="n">
-        <v>687407</v>
+        <v>234907</v>
       </c>
       <c r="P5" t="n">
-        <v>211667</v>
+        <v>80444</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999959468841553</v>
+        <v>0.9999977350234985</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9425992369651794</v>
+        <v>0.8968131542205811</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9240548610687256</v>
+        <v>0.8652767539024353</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9713125824928284</v>
+        <v>0.950742244720459</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9938051700592041</v>
+        <v>0.9878035187721252</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9872629046440125</v>
+        <v>0.9758543372154236</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963551163673401</v>
+        <v>0.9928489327430725</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48367</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>512041</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59802</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175016</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1287418</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1772729</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>799024</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181374</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300857</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735144376754761</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642943739891052</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838101863861084</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210821151733</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939042329788208</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983834028244019</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>56941</v>
+        <v>15797</v>
       </c>
       <c r="E6" t="n">
-        <v>89484</v>
+        <v>20687</v>
       </c>
       <c r="F6" t="n">
-        <v>109480</v>
+        <v>25313</v>
       </c>
       <c r="G6" t="n">
-        <v>228317</v>
+        <v>17556</v>
       </c>
       <c r="H6" t="n">
-        <v>46938</v>
+        <v>9018</v>
       </c>
       <c r="I6" t="n">
-        <v>4857</v>
+        <v>1124</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38939</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32230</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65403</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41916</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>1756</v>
+        <v>1359</v>
       </c>
       <c r="E7" t="n">
-        <v>76607</v>
+        <v>34502</v>
       </c>
       <c r="F7" t="n">
-        <v>349558</v>
+        <v>104712</v>
       </c>
       <c r="G7" t="n">
-        <v>144778</v>
+        <v>67960</v>
       </c>
       <c r="H7" t="n">
-        <v>2369440</v>
+        <v>275088</v>
       </c>
       <c r="I7" t="n">
-        <v>114583</v>
+        <v>26365</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4866</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178032</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45539</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>4396</v>
+        <v>2294</v>
       </c>
       <c r="F8" t="n">
-        <v>14245</v>
+        <v>6108</v>
       </c>
       <c r="G8" t="n">
-        <v>8761</v>
+        <v>5110</v>
       </c>
       <c r="H8" t="n">
-        <v>183976</v>
+        <v>66887</v>
       </c>
       <c r="I8" t="n">
-        <v>948358</v>
+        <v>112996</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
